--- a/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Forced Full Sync Config</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,54 +1177,76 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KW9EKY0E4316ZPDYJJSE2PJ2</t>
+          <t>h_01M48D9KEV9C5C5DBYDAP0H45P</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KW9EKY0E4316ZPDYJJSE2PJ2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01M48D9KEV9C5C5DBYDAP0H45P</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KW9EKY0E4316ZPDYJJSE2PJ2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KW9EKY0E4316ZPDYJJSE2PJ2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
